--- a/data/trans_camb/IP16B03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Estudios-trans_camb.xlsx
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,86</t>
+          <t>0,0; 53,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,02</t>
+          <t>0,0; 61,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,52</t>
+          <t>0,0; 35,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,06; 14,39</t>
+          <t>-69,8; 14,42</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 116,73</t>
+          <t>0,0; 116,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 117,48</t>
+          <t>0,0; 165,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,54</t>
+          <t>0,0; 54,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,0; 16,78</t>
+          <t>-73,09; 16,78</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>0,0; 40,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>0,0; 36,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 8,71</t>
+          <t>-16,88; 8,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 8,75</t>
+          <t>-17,86; 8,49</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,99</t>
+          <t>0,0; 68,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,0</t>
+          <t>0,0; 56,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 9,5</t>
+          <t>-16,93; 9,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 9,55</t>
+          <t>-18,33; 9,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Estudios-trans_camb.xlsx
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,88</t>
+          <t>0,0; 53,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,99</t>
+          <t>0,0; 54,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,3</t>
+          <t>0,0; 34,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 14,42</t>
+          <t>-69,8; 14,45</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 116,83</t>
+          <t>0,0; 114,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 165,62</t>
+          <t>0,0; 118,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,92</t>
+          <t>0,0; 53,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,09; 16,78</t>
+          <t>-73,81; 16,85</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,44</t>
+          <t>0,0; 36,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,2</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 8,69</t>
+          <t>-21,51; 8,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 8,49</t>
+          <t>-17,23; 8,77</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,54</t>
+          <t>0,0; 58,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,86</t>
+          <t>0,0; 60,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 9,48</t>
+          <t>-21,64; 9,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,28</t>
+          <t>-17,54; 9,6</t>
         </is>
       </c>
     </row>
